--- a/04_DESIGN_TABLES/DesignTable_2404_FINAL.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404_FINAL.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -7722,6 +7727,272 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>2404-40-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2404-14-12</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.4434</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G57" t="n">
+        <v>60</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="M57" t="n">
+        <v>37</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2404-14-12</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 3/16-12 x 3/4-14</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>3/4-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>1 3/16-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Carbon Steel</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Trivalent Cr3 Zinc</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>OMi-only SKU (absent from Air-Way); dropped by the 2026-09-23 crawl (adapters77 2026-10-16); L / hex / bores: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.6 on every cell; OMi and Brennan count as one source); JIC end MS33656J chain, NPTF end ASME + ENDL; bores: two published bores, step at the hex mid-plane</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L / hex / bores from OMi Items (= the Brennan TFA catalog p.6 on every cell, one source); end details from the end library</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>2404-14-12</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>OMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2404-16-08</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.5877</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G58" t="n">
+        <v>60</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="M58" t="n">
+        <v>37</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2404-16-08</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Male Connector, Male 37 deg Flare (JIC) x Male Pipe NPTF, 1 5/16-12 x 1/2-14</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>1/2-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Carbon Steel</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Trivalent Cr3 Zinc</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>OMi-only SKU (absent from Air-Way); dropped by the 2026-09-23 crawl (adapters77 2026-10-16); L / hex / bores: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.6 on every cell; OMi and Brennan count as one source); JIC end MS33656J chain, NPTF end ASME + ENDL; bores: two published bores, step at the hex mid-plane</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L / hex / bores from OMi Items (= the Brennan TFA catalog p.6 on every cell, one source); end details from the end library</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>2404-16-08</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2404_FINAL.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MeasuredAxial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeasuredAxial" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>0.54</v>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding) (2026-10-09)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding) (2026-10-09); D1@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS (2404.csv col 5 L); OMi file / Brennan 1.69) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09: overall length 1.69 from OMi (row 498; was 1.7, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.484 / pipe 0.281 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09: overall length 1.69 from OMi (row 498; was 1.7, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 0.484 / pipe 0.281 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 498 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | 2026-10-20 Air-Way first: D1@DRIVE OMi/Brennan 1.69 -&gt; Air-Way 1.7</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>2.375</v>
@@ -6013,12 +6013,12 @@
       </c>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding) (2026-10-09)</t>
+          <t>Brennan STEP measured == MS33656J published (VERIFIED) ; bores: OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding) (2026-10-09); D1@DRIVE: Air-Way 2.73 (raw 07_RAW_EXTRACTS (2404.csv col 5 L); OMi file / Brennan 2.74) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09: overall length 2.74 from OMi (row 520; was 2.73, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.937 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex)</t>
+          <t>2026-10-09: overall length 2.74 from OMi (row 520; was 2.73, question 26 / OMi first) ; 2026-10-09 Q-2404-BORE (user, from OMi: the hole is not the same throughout): two bores, JIC 1.078 / pipe 1.937 from OMi Side 1 / Side 2 ID, WebsitePartsInfo2026 row 520 (= Air-Way D / D1 to rounding); step at the hex mid-plane (Air-Way prints no depth, its drawing shows the step inside the hex) | 2026-10-20 Air-Way first: D1@DRIVE OMi/Brennan 2.74 -&gt; Air-Way 2.73</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2404_FINAL.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2404_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeasuredAxial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MeasuredAxial" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7612,7 +7612,9 @@
       <c r="C56" s="4" t="n">
         <v>2.875</v>
       </c>
-      <c r="D56" s="4" t="n"/>
+      <c r="D56" s="4" t="n">
+        <v>1.515</v>
+      </c>
       <c r="E56" s="4" t="n">
         <v>3.7528</v>
       </c>
@@ -7711,12 +7713,12 @@
       </c>
       <c r="AE56" s="4" t="inlineStr">
         <is>
-          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way)</t>
+          <t>Brennan product drawing 2026-09-05 (OMi-only SKU; absent from Air-Way) ; NPTF_ENDL 1.515: Brennan-measured -40 male NPTF end (gen_straight2 NPTF40_MEAS; 5404-40-40 / 5406-40-32 / 2501-40-40-FG STEPs, nptfm40.py; Q-NEW-ASME40) 2026-10-21</t>
         </is>
       </c>
       <c r="AF56" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED: NPTF -40 end length unmeasured</t>
+          <t>2026-10-21 batch 19 C (staged): NPTF_ENDL@DRIVE 1.515 = the Brennan-measured -40 end length of the end library (Q-NEW-ASME40) - was: BLOCKED: NPTF -40 end length unmeasured</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
